--- a/documents/fiche_de_personnage_2026.xlsx
+++ b/documents/fiche_de_personnage_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julien\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F5DC6E-6E8D-419A-B7BD-8AE16D70553A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844D98B1-0950-47FC-A921-76F634990CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{2CCEA79F-E9EC-0C42-8879-50C18F95B055}"/>
   </bookViews>
@@ -479,8 +479,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -524,23 +539,8 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -955,20 +955,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="61.5" x14ac:dyDescent="0.85">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:7" ht="33" x14ac:dyDescent="0.45">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="2"/>
@@ -991,9 +991,9 @@
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
     </row>
     <row r="7" spans="1:7" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
@@ -1033,7 +1033,7 @@
       <c r="C10" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="16"/>
+      <c r="D10" s="36"/>
     </row>
     <row r="11" spans="1:7" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
@@ -1047,12 +1047,12 @@
     </row>
     <row r="12" spans="1:7" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:7" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
     </row>
     <row r="14" spans="1:7" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
@@ -1069,7 +1069,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="31">
+      <c r="A15" s="17">
         <v>1</v>
       </c>
       <c r="B15" s="6"/>
@@ -1078,13 +1078,13 @@
       <c r="G15"/>
     </row>
     <row r="16" spans="1:7" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="31"/>
+      <c r="A16" s="17"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
     </row>
     <row r="17" spans="1:8" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="34">
+      <c r="A17" s="18">
         <v>2</v>
       </c>
       <c r="B17" s="8"/>
@@ -1092,13 +1092,13 @@
       <c r="D17" s="8"/>
     </row>
     <row r="18" spans="1:8" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="34"/>
+      <c r="A18" s="18"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
     </row>
     <row r="19" spans="1:8" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="31">
+      <c r="A19" s="17">
         <v>3</v>
       </c>
       <c r="B19" s="6"/>
@@ -1106,13 +1106,13 @@
       <c r="D19" s="6"/>
     </row>
     <row r="20" spans="1:8" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="31"/>
+      <c r="A20" s="17"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
     </row>
     <row r="21" spans="1:8" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="34">
+      <c r="A21" s="18">
         <v>4</v>
       </c>
       <c r="B21" s="8"/>
@@ -1120,13 +1120,13 @@
       <c r="D21" s="8"/>
     </row>
     <row r="22" spans="1:8" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
+      <c r="A22" s="18"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
     </row>
     <row r="23" spans="1:8" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="31">
+      <c r="A23" s="17">
         <v>5</v>
       </c>
       <c r="B23" s="6"/>
@@ -1134,16 +1134,16 @@
       <c r="D23" s="6"/>
     </row>
     <row r="24" spans="1:8" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="31"/>
+      <c r="A24" s="17"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
       <c r="D24" s="14"/>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="19"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="24"/>
     </row>
     <row r="25" spans="1:8" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
@@ -1151,90 +1151,97 @@
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="6"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="22"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="27"/>
     </row>
     <row r="26" spans="1:8" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="9"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="22"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="27"/>
     </row>
     <row r="27" spans="1:8" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="36" t="s">
+      <c r="A27" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="22"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="27"/>
     </row>
     <row r="28" spans="1:8" s="5" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="35"/>
-      <c r="B28" s="35"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="22"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="27"/>
     </row>
     <row r="29" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="35"/>
-      <c r="B29" s="35"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="22"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="27"/>
     </row>
     <row r="30" spans="1:8" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="35"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="22"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="27"/>
     </row>
     <row r="31" spans="1:8" s="5" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="35"/>
-      <c r="B31" s="35"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="22"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="27"/>
     </row>
     <row r="32" spans="1:8" s="5" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="31"/>
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="26"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="31"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A33" s="33" t="s">
+      <c r="A33" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="33"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H32"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A17:A18"/>
@@ -1251,13 +1258,6 @@
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="A30:B30"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H32"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="C30:D30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
